--- a/output/pdf_financials_xlsx/ALY.xlsx
+++ b/output/pdf_financials_xlsx/ALY.xlsx
@@ -5791,40 +5791,40 @@
         <v>0</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.032088</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>0.1412</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>0.320544</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.314549</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.116446</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>0.353046</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>0.232066</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>0.229186</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>0.208387</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>0.25165</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>0.251764</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>0.271469</v>
       </c>
     </row>
     <row r="92">
@@ -5846,43 +5846,43 @@
         <v>0.568327</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.568327</v>
+        <v>0.3519</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.390801</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.820413</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.544417</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.177697</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.72323</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.671486</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.687466</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.108862</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.053985</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.22637</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.645585</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.048989</v>
       </c>
     </row>
     <row r="93">
@@ -9888,7 +9888,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10062,7 +10066,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11762,7 +11770,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -12847,7 +12859,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -15344,7 +15360,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -15546,7 +15566,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -16144,7 +16168,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -16346,7 +16374,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ALY.xlsx
+++ b/output/pdf_financials_xlsx/ALY.xlsx
@@ -939,43 +939,43 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.004313</v>
+        <v>1.368234</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.037229</v>
+        <v>2.821138</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.108989</v>
+        <v>3.546243</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.088752</v>
+        <v>2.239761</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.079503</v>
+        <v>1.657005</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.280137</v>
+        <v>3.40515</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.4169</v>
+        <v>3.324556</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.573563</v>
+        <v>3.170276</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.243774</v>
+        <v>2.816661</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.278018</v>
+        <v>3.924384</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.355213</v>
+        <v>4.074649</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.128449</v>
+        <v>3.332796</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.011115</v>
+        <v>1.968102</v>
       </c>
     </row>
     <row r="11">
@@ -2412,40 +2412,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.031815</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.108526</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.108526</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.479575</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.75973</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.925829</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.195529</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.346867</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.292352</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.35706</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.051618</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.354612</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1.669621</v>
@@ -2528,40 +2528,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.031815</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.108526</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.108526</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.479575</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.75973</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.925829</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.195529</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.346867</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.292352</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.35706</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.051618</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.354612</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1.669621</v>
@@ -3224,40 +3224,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.284518</v>
+        <v>0.252703</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.241287</v>
+        <v>0.132761</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.241287</v>
+        <v>0.132761</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.505063</v>
+        <v>0.025488</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.802764</v>
+        <v>0.043034</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.967634</v>
+        <v>0.041805</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2696</v>
+        <v>0.074071</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.447543</v>
+        <v>0.100676</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.294584</v>
+        <v>0.002232</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.444553</v>
+        <v>0.087493</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.260366</v>
+        <v>0.208748</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.557759</v>
+        <v>0.203147</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.204004</v>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -20473,7 +20473,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -54616,7 +54616,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -54788,7 +54788,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">

--- a/output/pdf_financials_xlsx/ALY.xlsx
+++ b/output/pdf_financials_xlsx/ALY.xlsx
@@ -2125,7 +2125,7 @@
         <v>0.004842</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.188795</v>
+        <v>0.184217</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.213874</v>
@@ -2134,19 +2134,19 @@
         <v>0.221624</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.443722</v>
+        <v>0.423865</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.5068510000000001</v>
+        <v>0.480709</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.5101830000000001</v>
+        <v>0.492251</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.62132</v>
+        <v>0.497595</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.22311</v>
+        <v>0.106673</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.08548</v>
@@ -2185,7 +2185,7 @@
         <v>-2.826294</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.6831660000000001</v>
+        <v>-0.687744</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-2.866815</v>
@@ -2194,19 +2194,19 @@
         <v>-0.596306</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.420616</v>
+        <v>-0.440473</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.794687</v>
+        <v>-1.820829</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.159775</v>
+        <v>-1.177707</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.358877</v>
+        <v>-1.482602</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.858766</v>
+        <v>-3.975203</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-4.084185</v>
@@ -2245,7 +2245,7 @@
         <v>-174.8890195229108</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-100.371711164264</v>
+        <v>-101.0443173737504</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-630.3144300090364</v>
@@ -2254,19 +2254,19 @@
         <v>-55.45232292027984</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-9.312340994947926</v>
+        <v>-9.751970384074067</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-37.09710325479985</v>
+        <v>-37.63747183900811</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-31.57813769922251</v>
+        <v>-32.06638685550063</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-42.74855627984058</v>
+        <v>-46.64078870832621</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-128.5687059652967</v>
+        <v>-132.4482245514149</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>-244.2424133693341</v>
@@ -6265,28 +6265,28 @@
         <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.184217</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.213874</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.221624</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.423865</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.480709</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.492251</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.497595</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.106673</v>
       </c>
       <c r="P100" s="3" t="n">
         <v>0</v>
@@ -28690,7 +28690,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -32490,7 +32490,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -35686,7 +35686,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -40387,7 +40387,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -43092,7 +43092,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
